--- a/stories/arbres/ATOM-DIF.PAR.001-05.xlsx
+++ b/stories/arbres/ATOM-DIF.PAR.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Faustine est au jardin avec maman. Marceau est près du bac. Il parle peu. Faustine veut jouer. Maman dit : on peut attendre. On n'imite pas. On peut tendre un jouet. On ne force pas la parole. Faustine tend le seau. Elle attend. Marceau touche le seau. Il ne dit rien. Faustine sourit. Elle ne force pas la parole. Plus tard, Marceau dit : sable.</t>
+          <t>Faustine est au jardin avec maman. Marceau est près du bac. Il parle peu. Faustine veut jouer. On peut attendre. On n'imite pas. On peut tendre un jouet. On ne force pas la parole. Faustine tend le seau. Elle attend. Marceau touche le seau. Il ne dit rien. Faustine sourit. Elle ne force pas la parole. Plus tard, Sable.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Faustine est au jardin avec maman. Marceau est près du bac. Il parle peu. Faustine veut jouer.
+maman|On peut attendre. On n'imite pas. On peut tendre un jouet. On ne force pas la parole.
+narrateur|Faustine tend le seau. Elle attend. Marceau touche le seau. Il ne dit rien. Faustine sourit. Elle ne force pas la parole. Plus tard,
+copain|Sable.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1489,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Marceau parle peu. Que fait Faustine ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1662,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Faustine a su attendre. Elle a tendu un jouet. Elle n'a pas forcé la parole.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1829,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman range le seau. Faustine donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1996,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2036,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.PAR.001-05.xlsx
+++ b/stories/arbres/ATOM-DIF.PAR.001-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,7 @@
 copain|Sable.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1496,6 +1502,7 @@
           <t>narrateur|Marceau parle peu. Que fait Faustine ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1667,6 +1674,7 @@
           <t>narrateur|Faustine a su attendre. Elle a tendu un jouet. Elle n'a pas forcé la parole.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1834,6 +1842,7 @@
           <t>narrateur|Maman range le seau. Faustine donne la main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2001,6 +2010,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2019,7 +2029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2053,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2244,6 +2268,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-DIF.PAR.001-05.xlsx
+++ b/stories/arbres/ATOM-DIF.PAR.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Faustine tend un jouet et attend</t>
+          <t>Le seau tiède du jardin</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DIF.BES.002</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un seau bleu tiède attend près du bac du jardin. Nina le tend à Raphaël, qui parle peu. Ils versent le sable près des pots.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Faustine est au jardin avec maman. Marceau est près du bac. Il parle peu. Faustine veut jouer. On peut attendre. On n'imite pas. On peut tendre un jouet. On ne force pas la parole. Faustine tend le seau. Elle attend. Marceau touche le seau. Il ne dit rien. Faustine sourit. Elle ne force pas la parole. Plus tard, Sable.</t>
+          <t>Les tomates du jardin sont encore vertes. Une abeille tourne près du romarin. Ça sent le thym et la terre chaude. Le seau bleu est tiède au soleil. Papa arrose les pots. L'eau fait un bruit fin. Maman pose un chapeau de paille. Tu as vu l'abeille, Nina ? Elle tourne. Le romarin sent fort, hein ? Oui, maman. En ce moment, Nina s'agenouille près du bac. Le bac est en bois. Le sable du jardin est un peu gris. Raphaël est déjà là. Il parle peu. Il regarde une coccinelle sur le rebord. Nina a envie de jouer. On peut attendre. On n'imite pas. On peut tendre un jouet. On ne force pas la parole. Le seau bleu est tiède. Tu peux le tendre. Je tends le seau. Nina tend le seau. Elle attend. Raphaël touche le seau. Il ne dit rien. Nina reste à genoux. Un grain de sable colle à son genou. Raphaël prend le seau. Il le remplit près des pots. Bravo, Nina. Tu as su attendre. C'est du bon travail. Tu as tendu un jouet. Nina pose une pelle à côté. Raphaël verse le seau. Un petit tas grandit entre les pots. Raphaël ne parle toujours pas. C'est possible. On peut attendre. On ne force pas la parole. Regarder, c'est bien aussi. Un silence. Puis Raphaël dit tout bas. Terre. Terre. Ils jouent. Plus tard, maman apporte une gourde. Un peu d'eau ? Raphaël secoue la tête. D'accord. D'accord. Regarder, c'est bien aussi. Tu as fini le tas, Nina ? Pas encore. Nina attend encore. Raphaël ajoute une pelle. Le jeu a eu lieu, même avec peu de mots.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,10 +1329,67 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Faustine est au jardin avec maman. Marceau est près du bac. Il parle peu. Faustine veut jouer.
-maman|On peut attendre. On n'imite pas. On peut tendre un jouet. On ne force pas la parole.
-narrateur|Faustine tend le seau. Elle attend. Marceau touche le seau. Il ne dit rien. Faustine sourit. Elle ne force pas la parole. Plus tard,
-copain|Sable.</t>
+          <t>narrateur|Les tomates du jardin sont encore vertes.
+narrateur|Une abeille tourne près du romarin.
+narrateur|Ça sent le thym et la terre chaude.
+narrateur|Le seau bleu est tiède au soleil.
+narrateur|Papa arrose les pots.
+narrateur|L'eau fait un bruit fin.
+narrateur|Maman pose un chapeau de paille.
+papa|Tu as vu l'abeille, Nina ?
+enfant-f|Elle tourne.
+maman|Le romarin sent fort, hein ?
+enfant-f|Oui, maman.
+narrateur|En ce moment, Nina s'agenouille près du bac.
+narrateur|Le bac est en bois.
+narrateur|Le sable du jardin est un peu gris.
+narrateur|Raphaël est déjà là.
+narrateur|Il parle peu.
+narrateur|Il regarde une coccinelle sur le rebord.
+narrateur|Nina a envie de jouer.
+maman|On peut attendre.
+maman|On n'imite pas.
+maman|On peut tendre un jouet.
+maman|On ne force pas la parole.
+papa|Le seau bleu est tiède.
+papa|Tu peux le tendre.
+enfant-f|Je tends le seau.
+narrateur|Nina tend le seau.
+narrateur|Elle attend.
+narrateur|Raphaël touche le seau.
+narrateur|Il ne dit rien.
+narrateur|Nina reste à genoux.
+narrateur|Un grain de sable colle à son genou.
+narrateur|Raphaël prend le seau.
+narrateur|Il le remplit près des pots.
+papa|Bravo, Nina.
+papa|Tu as su attendre.
+maman|C'est du bon travail.
+maman|Tu as tendu un jouet.
+narrateur|Nina pose une pelle à côté.
+narrateur|Raphaël verse le seau.
+narrateur|Un petit tas grandit entre les pots.
+narrateur|Raphaël ne parle toujours pas.
+narrateur|C'est possible.
+maman|On peut attendre.
+maman|On ne force pas la parole.
+papa|Regarder, c'est bien aussi.
+narrateur|Un silence.
+narrateur|Puis Raphaël dit tout bas.
+narrateur|Terre.
+enfant-f|Terre.
+narrateur|Ils jouent.
+narrateur|Plus tard, maman apporte une gourde.
+maman|Un peu d'eau ?
+narrateur|Raphaël secoue la tête.
+enfant-f|D'accord.
+papa|D'accord.
+papa|Regarder, c'est bien aussi.
+maman|Tu as fini le tas, Nina ?
+enfant-f|Pas encore.
+narrateur|Nina attend encore.
+narrateur|Raphaël ajoute une pelle.
+narrateur|Le jeu a eu lieu, même avec peu de mots.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1343,7 +1417,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Marceau parle peu. Que fait Faustine ?</t>
+          <t>Raphaël parle peu. Que fait Nina ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1499,7 +1573,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Marceau parle peu. Que fait Faustine ?</t>
+          <t>narrateur|Raphaël parle peu.
+narrateur|Que fait Nina ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1527,7 +1602,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Faustine a su attendre. Elle a tendu un jouet. Elle n'a pas forcé la parole.</t>
+          <t>Nina a su attendre. Elle a tendu un jouet. Elle n'a pas forcé la parole. Bravo, Nina. Tu as fait du bon travail. Tu as tendu le seau ? Oui. J'ai attendu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1671,7 +1746,14 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Faustine a su attendre. Elle a tendu un jouet. Elle n'a pas forcé la parole.</t>
+          <t>narrateur|Nina a su attendre.
+narrateur|Elle a tendu un jouet.
+narrateur|Elle n'a pas forcé la parole.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|Tu as tendu le seau ?
+enfant-f|Oui.
+enfant-f|J'ai attendu.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1699,7 +1781,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman range le seau. Faustine donne la main.</t>
+          <t>Maman range le seau bleu. Papa ferme le robinet. L'eau s'arrête. Nina donne la main. On laisse le tas ? Il reste près des pots. Bravo. L'abeille s'éloigne. Les tomates restent vertes.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1839,7 +1921,15 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman range le seau. Faustine donne la main.</t>
+          <t>narrateur|Maman range le seau bleu.
+narrateur|Papa ferme le robinet.
+narrateur|L'eau s'arrête.
+narrateur|Nina donne la main.
+maman|On laisse le tas ?
+enfant-f|Il reste près des pots.
+papa|Bravo.
+narrateur|L'abeille s'éloigne.
+narrateur|Les tomates restent vertes.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1867,7 +1957,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai tendu le seau. On a fait un tas. Bravo. Tu as fait du bon travail. On a su attendre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2007,7 +2097,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai tendu le seau.
+enfant-f|On a fait un tas.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+papa|On a su attendre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2029,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2067,6 +2162,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.PAR.001-05.xlsx
+++ b/stories/arbres/ATOM-DIF.PAR.001-05.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le seau tiède du jardin</t>
+          <t>Le haricot sous la buée</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Un seau bleu tiède attend près du bac du jardin. Nina le tend à Raphaël, qui parle peu. Ils versent le sable près des pots.</t>
+          <t>Nina veut planter un haricot sous le châssis embué. Raphaël parle peu. Elle lui tend la petite pelle. Ils font un trou. Le haricot disparaît sous la terre tiède.</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les tomates du jardin sont encore vertes. Une abeille tourne près du romarin. Ça sent le thym et la terre chaude. Le seau bleu est tiède au soleil. Papa arrose les pots. L'eau fait un bruit fin. Maman pose un chapeau de paille. Tu as vu l'abeille, Nina ? Elle tourne. Le romarin sent fort, hein ? Oui, maman. En ce moment, Nina s'agenouille près du bac. Le bac est en bois. Le sable du jardin est un peu gris. Raphaël est déjà là. Il parle peu. Il regarde une coccinelle sur le rebord. Nina a envie de jouer. On peut attendre. On n'imite pas. On peut tendre un jouet. On ne force pas la parole. Le seau bleu est tiède. Tu peux le tendre. Je tends le seau. Nina tend le seau. Elle attend. Raphaël touche le seau. Il ne dit rien. Nina reste à genoux. Un grain de sable colle à son genou. Raphaël prend le seau. Il le remplit près des pots. Bravo, Nina. Tu as su attendre. C'est du bon travail. Tu as tendu un jouet. Nina pose une pelle à côté. Raphaël verse le seau. Un petit tas grandit entre les pots. Raphaël ne parle toujours pas. C'est possible. On peut attendre. On ne force pas la parole. Regarder, c'est bien aussi. Un silence. Puis Raphaël dit tout bas. Terre. Terre. Ils jouent. Plus tard, maman apporte une gourde. Un peu d'eau ? Raphaël secoue la tête. D'accord. D'accord. Regarder, c'est bien aussi. Tu as fini le tas, Nina ? Pas encore. Nina attend encore. Raphaël ajoute une pelle. Le jeu a eu lieu, même avec peu de mots.</t>
+          <t>La vitre du châssis est toute embuée. Un doigt y a dessiné un petit rond. Ça sent le thym et la terre chaude. Une abeille passe près du romarin. Les pots sont encore humides. Papa arrose les pots. L'eau fait un bruit fin. Maman pose un chapeau de paille. Le chapeau sent le soleil. Tu as vu le rond, Nina ? Il est sur la buée. Le thym sent fort, hein ? Oui, maman. Je veux planter un haricot. Sous le châssis. Un haricot à lui, tout seul ? Oui. Dans un petit trou. En ce moment, Nina s'agenouille. La petite pelle est lisse. Le haricot est dans sa poche. Il fait un petit bruit. Raphaël est déjà là. Il parle peu. Il regarde une coccinelle sur le rebord. La coccinelle est rouge et ronde. Nina a envie de tout expliquer. On peut attendre. Tu peux tendre un jouet. Nina tient la petite pelle. Raphaël ne dit rien.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Faustine est au jardin avec maman. Marceau est près du bac. Il parle peu. Faustine veut jouer. Maman dit : on peut &lt;emphasis level="moderate"&gt;attendre&lt;/emphasis&gt;. On n'imite pas. On peut tendre un jouet. On ne force pas la parole. Faustine tend le seau. Elle attend. Marceau touche le seau. Il ne dit rien. Faustine sourit. Elle ne force pas la parole. Plus tard, Marceau dit : sable.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La vitre du châssis est toute embuée. Un doigt y a dessiné un petit rond. Ça sent le thym et la terre chaude. Une abeille passe près du romarin. Les pots sont encore humides. Papa arrose les pots. L'eau fait un bruit fin. Maman pose un chapeau de paille. Le chapeau sent le soleil. Tu as vu le rond, Nina ? Il est sur la buée. Le thym sent fort, hein ? Oui, maman. Je veux planter un haricot. Sous le châssis. Un haricot à lui, tout seul ? Oui. Dans un petit trou. En ce moment, Nina s'agenouille. La petite pelle est lisse. Le haricot est dans sa poche. Il fait un petit bruit. Raphaël est déjà là. Il parle peu. Il regarde une coccinelle sur le rebord. La coccinelle est rouge et ronde. Nina a envie de tout expliquer. On peut attendre. Tu peux tendre un jouet. Nina tient la petite pelle. Raphaël ne dit rien.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1329,70 +1329,39 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Les tomates du jardin sont encore vertes.
-narrateur|Une abeille tourne près du romarin.
+          <t>narrateur|La vitre du châssis est toute embuée.
+narrateur|Un doigt y a dessiné un petit rond.
 narrateur|Ça sent le thym et la terre chaude.
-narrateur|Le seau bleu est tiède au soleil.
+narrateur|Une abeille passe près du romarin.
+narrateur|Les pots sont encore humides.
 narrateur|Papa arrose les pots.
 narrateur|L'eau fait un bruit fin.
 narrateur|Maman pose un chapeau de paille.
-papa|Tu as vu l'abeille, Nina ?
-enfant-f|Elle tourne.
-maman|Le romarin sent fort, hein ?
+narrateur|Le chapeau sent le soleil.
+papa|Tu as vu le rond, Nina ?
+enfant-f|Il est sur la buée.
+maman|Le thym sent fort, hein ?
 enfant-f|Oui, maman.
-narrateur|En ce moment, Nina s'agenouille près du bac.
-narrateur|Le bac est en bois.
-narrateur|Le sable du jardin est un peu gris.
+enfant-f|Je veux planter un haricot.
+enfant-f|Sous le châssis.
+papa|Un haricot à lui, tout seul ?
+enfant-f|Oui.
+enfant-f|Dans un petit trou.
+narrateur|En ce moment, Nina s'agenouille.
+narrateur|La petite pelle est lisse.
+narrateur|Le haricot est dans sa poche.
+narrateur|Il fait un petit bruit.
 narrateur|Raphaël est déjà là.
 narrateur|Il parle peu.
 narrateur|Il regarde une coccinelle sur le rebord.
-narrateur|Nina a envie de jouer.
+narrateur|La coccinelle est rouge et ronde.
+narrateur|Nina a envie de tout expliquer.
 maman|On peut attendre.
-maman|On n'imite pas.
-maman|On peut tendre un jouet.
-maman|On ne force pas la parole.
-papa|Le seau bleu est tiède.
-papa|Tu peux le tendre.
-enfant-f|Je tends le seau.
-narrateur|Nina tend le seau.
-narrateur|Elle attend.
-narrateur|Raphaël touche le seau.
-narrateur|Il ne dit rien.
-narrateur|Nina reste à genoux.
-narrateur|Un grain de sable colle à son genou.
-narrateur|Raphaël prend le seau.
-narrateur|Il le remplit près des pots.
-papa|Bravo, Nina.
-papa|Tu as su attendre.
-maman|C'est du bon travail.
-maman|Tu as tendu un jouet.
-narrateur|Nina pose une pelle à côté.
-narrateur|Raphaël verse le seau.
-narrateur|Un petit tas grandit entre les pots.
-narrateur|Raphaël ne parle toujours pas.
-narrateur|C'est possible.
-maman|On peut attendre.
-maman|On ne force pas la parole.
-papa|Regarder, c'est bien aussi.
-narrateur|Un silence.
-narrateur|Puis Raphaël dit tout bas.
-narrateur|Terre.
-enfant-f|Terre.
-narrateur|Ils jouent.
-narrateur|Plus tard, maman apporte une gourde.
-maman|Un peu d'eau ?
-narrateur|Raphaël secoue la tête.
-enfant-f|D'accord.
-papa|D'accord.
-papa|Regarder, c'est bien aussi.
-maman|Tu as fini le tas, Nina ?
-enfant-f|Pas encore.
-narrateur|Nina attend encore.
-narrateur|Raphaël ajoute une pelle.
-narrateur|Le jeu a eu lieu, même avec peu de mots.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+papa|Tu peux tendre un jouet.
+narrateur|Nina tient la petite pelle.
+narrateur|Raphaël ne dit rien.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1422,7 +1391,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Marceau parle peu. Que fait Faustine ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël parle peu. Que fait Nina ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1437,7 +1406,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>attendre | tendre | le seau | un jouet</t>
+          <t>attendre | tendre | la pelle | un jouet | elle attend</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1452,7 +1421,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle tend un jouet. Elle fait quoi encore ?</t>
+          <t>Elle tend un jouet. Elle attend. Que fait Nina ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1501,7 +1470,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1577,7 +1546,6 @@
 narrateur|Que fait Nina ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1602,12 +1570,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nina a su attendre. Elle a tendu un jouet. Elle n'a pas forcé la parole. Bravo, Nina. Tu as fait du bon travail. Tu as tendu le seau ? Oui. J'ai attendu.</t>
+          <t>Nina tend la petite pelle. Pour le trou. Elle attend. Un grain de terre colle à son genou. Raphaël touche la pelle. Il ne dit rien. On ne force pas la parole. La terre n'a pas besoin de mots. Raphaël prend la pelle. Il creuse près du thym. Nina pose le haricot. Il est lisse et un peu froid. Raphaël recouvre. La terre est tiède. Elle sent le jardin. Un peu l'eau. Un peu le thym. Il est caché. Puis Raphaël dit tout bas. Haricot. Haricot. Tu as su attendre. Bravo, Nina. Papa verse un peu d'eau. La terre devient sombre. Une petite flaque brille, puis s'en va.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Faustine a su &lt;emphasis level="moderate"&gt;attendre&lt;/emphasis&gt;. Elle a tendu un jouet. Elle n'a pas forcé la parole.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina tend la petite pelle. Pour le trou. Elle attend. Un grain de terre colle à son genou. Raphaël touche la pelle. Il ne dit rien. On ne force pas la parole. La terre n'a pas besoin de mots. Raphaël prend la pelle. Il creuse près du thym. Nina pose le haricot. Il est lisse et un peu froid. Raphaël recouvre. La terre est tiède. Elle sent le jardin. Un peu l'eau. Un peu le thym. Il est caché. Puis Raphaël dit tout bas. Haricot. Haricot. Tu as su attendre. Bravo, Nina. Papa verse un peu d'eau. La terre devient sombre. Une petite flaque brille, puis s'en va.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1670,7 +1638,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1746,17 +1714,34 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nina a su attendre.
-narrateur|Elle a tendu un jouet.
-narrateur|Elle n'a pas forcé la parole.
-maman|Bravo, Nina.
-maman|Tu as fait du bon travail.
-papa|Tu as tendu le seau ?
-enfant-f|Oui.
-enfant-f|J'ai attendu.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nina tend la petite pelle.
+enfant-f|Pour le trou.
+narrateur|Elle attend.
+narrateur|Un grain de terre colle à son genou.
+narrateur|Raphaël touche la pelle.
+narrateur|Il ne dit rien.
+maman|On ne force pas la parole.
+papa|La terre n'a pas besoin de mots.
+narrateur|Raphaël prend la pelle.
+narrateur|Il creuse près du thym.
+narrateur|Nina pose le haricot.
+narrateur|Il est lisse et un peu froid.
+narrateur|Raphaël recouvre.
+narrateur|La terre est tiède.
+narrateur|Elle sent le jardin.
+narrateur|Un peu l'eau.
+narrateur|Un peu le thym.
+enfant-f|Il est caché.
+narrateur|Puis Raphaël dit tout bas.
+enfant-m|Haricot.
+enfant-f|Haricot.
+papa|Tu as su attendre.
+papa|Bravo, Nina.
+narrateur|Papa verse un peu d'eau.
+narrateur|La terre devient sombre.
+narrateur|Une petite flaque brille, puis s'en va.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1781,12 +1766,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman range le seau bleu. Papa ferme le robinet. L'eau s'arrête. Nina donne la main. On laisse le tas ? Il reste près des pots. Bravo. L'abeille s'éloigne. Les tomates restent vertes.</t>
+          <t>Maman essuie un peu la buée. Le rond a disparu. On voit le haricot caché, presque. Un peu d'eau, pour toi ? Raphaël secoue la tête. D'accord. D'accord. Tu as fini le trou, Nina ? Oui, maman. Le haricot est dessous. Papa ferme le robinet. L'eau s'arrête. Nina donne la main. Le chapeau de paille reste sur le banc. La coccinelle s'en va. Le thym sent encore. L'abeille s'éloigne. Le thym reste. Oui. Il sent encore.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman range le seau. Faustine donne la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman essuie un peu la buée. Le rond a disparu. On voit le haricot caché, presque. Un peu d'eau, pour toi ? Raphaël secoue la tête. D'accord. D'accord. Tu as fini le trou, Nina ? Oui, maman. Le haricot est dessous. Papa ferme le robinet. L'eau s'arrête. Nina donne la main. Le chapeau de paille reste sur le banc. La coccinelle s'en va. Le thym sent encore. L'abeille s'éloigne. Le thym reste. Oui. Il sent encore.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1849,7 +1834,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1921,18 +1906,28 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman range le seau bleu.
+          <t>narrateur|Maman essuie un peu la buée.
+narrateur|Le rond a disparu.
+narrateur|On voit le haricot caché, presque.
+maman|Un peu d'eau, pour toi ?
+narrateur|Raphaël secoue la tête.
+enfant-f|D'accord.
+papa|D'accord.
+maman|Tu as fini le trou, Nina ?
+enfant-f|Oui, maman.
+enfant-f|Le haricot est dessous.
 narrateur|Papa ferme le robinet.
 narrateur|L'eau s'arrête.
 narrateur|Nina donne la main.
-maman|On laisse le tas ?
-enfant-f|Il reste près des pots.
-papa|Bravo.
+narrateur|Le chapeau de paille reste sur le banc.
+papa|La coccinelle s'en va.
+narrateur|Le thym sent encore.
 narrateur|L'abeille s'éloigne.
-narrateur|Les tomates restent vertes.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+enfant-f|Le thym reste.
+papa|Oui.
+papa|Il sent encore.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,12 +1952,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai tendu le seau. On a fait un tas. Bravo. Tu as fait du bon travail. On a su attendre. L'histoire est finie.</t>
+          <t>Le haricot est sous la terre. Sous le châssis. Il a de l'eau, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le haricot est sous la terre. Sous le châssis. Il a de l'eau, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2018,14 +2013,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2097,15 +2092,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-f|J'ai tendu le seau.
-enfant-f|On a fait un tas.
-maman|Bravo.
-maman|Tu as fait du bon travail.
-papa|On a su attendre.
+          <t>enfant-f|Le haricot est sous la terre.
+maman|Sous le châssis.
+papa|Il a de l'eau, maintenant.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2124,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2169,6 +2161,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.PAR.001-05.xlsx
+++ b/stories/arbres/ATOM-DIF.PAR.001-05.xlsx
@@ -1952,12 +1952,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le haricot est sous la terre. Sous le châssis. Il a de l'eau, maintenant. L'histoire est finie.</t>
+          <t>Le haricot est sous la terre. Sous le châssis. Il a de l'eau, maintenant.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Le haricot est sous la terre. Sous le châssis. Il a de l'eau, maintenant. L'histoire est finie.</t>
+          <t>Le haricot est sous la terre. Sous le châssis. Il a de l'eau, maintenant.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2094,8 +2094,7 @@
         <is>
           <t>enfant-f|Le haricot est sous la terre.
 maman|Sous le châssis.
-papa|Il a de l'eau, maintenant.
-narrateur|L'histoire est finie.</t>
+papa|Il a de l'eau, maintenant.</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2166,6 +2165,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-DIF.PAR.001-05.xlsx
+++ b/stories/arbres/ATOM-DIF.PAR.001-05.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin</t>
+          <t>jardin, châssis, thym</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Faustine, Marceau, maman</t>
+          <t>Nina, Raphaël, papa, maman</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.PAR.001-05.xlsx
+++ b/stories/arbres/ATOM-DIF.PAR.001-05.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le haricot sous la buée</t>
+          <t>Le seau tiède du jardin</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin, châssis, thym</t>
+          <t>jardin, tomates vertes, abeille, romarin, thym, seau bleu tiède, pots, terre</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nina veut planter un haricot sous le châssis embué. Raphaël parle peu. Elle lui tend la petite pelle. Ils font un trou. Le haricot disparaît sous la terre tiède.</t>
+          <t>Une goutte tiède pend au romarin. Sur une feuille, un éclat de romarin brille. Nina veut le seau, maintenant. Raphaël ne dit rien. Elle pousse trop vite, eau. Sourire parti, poitrine, papa accroupi. Elle refuse de foncer, tend le seau, attend. Merci vécu. 2e ruse, Dis-le. Un éclat de romarin tient près des tomates.</t>
         </is>
       </c>
     </row>
@@ -1189,17 +1189,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La vitre du châssis est toute embuée. Un doigt y a dessiné un petit rond. Ça sent le thym et la terre chaude. Une abeille passe près du romarin. Les pots sont encore humides. Papa arrose les pots. L'eau fait un bruit fin. Maman pose un chapeau de paille. Le chapeau sent le soleil. Tu as vu le rond, Nina ? Il est sur la buée. Le thym sent fort, hein ? Oui, maman. Je veux planter un haricot. Sous le châssis. Un haricot à lui, tout seul ? Oui. Dans un petit trou. En ce moment, Nina s'agenouille. La petite pelle est lisse. Le haricot est dans sa poche. Il fait un petit bruit. Raphaël est déjà là. Il parle peu. Il regarde une coccinelle sur le rebord. La coccinelle est rouge et ronde. Nina a envie de tout expliquer. On peut attendre. Tu peux tendre un jouet. Nina tient la petite pelle. Raphaël ne dit rien.</t>
+          <t>Une goutte tiède pend au romarin. Elle tremble, puis tient. Elle est chaude, papa. Tu la vois, Nina ? Oui, papa. Les tomates sont vertes, sous les feuilles. Elles sont dures, maman. Tu les as touchées, Nina ? Oui, maman. Sur une feuille, un éclat de romarin brille. Il brille, papa. Tu le vois, le petit point ? Oui, un petit point. Ça sent le thym, tout près. Ça pique le nez. Le thym est fort, Nina ? Oui, maman. Une abeille passe près des tomates. Elle fait un bruit, papa. Près des fleurs ? Oui, tout près. Le seau bleu attend au bord de la terre. Le plastique est tiède, contre la paume. Il est chaud, maman. Tu le tiens, Nina ? Oui. En ce moment, Nina pose le seau. Je veux le seau, maintenant ! Pour les tomates, tout de suite. De l'eau, là ? Oui, de l'eau. Le seau bleu est plein ? Presque. Raphaël arrive près des pots. Il marche sans bruit. Tu verses avec moi ? Raphaël ne dit rien. Il regarde ses mains. Nina a envie de tout expliquer. Les mots montent très vite. Le seau ! L'eau ! Les tomates ! Nina pousse trop vite vers lui. Le seau penche. L'eau tombe sur la terre. Oh. Le sourire de Nina disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Ses épaules tombent un peu. Papa s'accroupit à la même hauteur. Tu vois Raphaël, Nina ? Oui, papa. Tes mains tiennent le seau, Nina ? Un peu, maman. L'éclat de romarin tremble, puis tient. Raphaël reste près des pots. Il ne dit rien, papa. Nina regarde papa.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>La vitre du châssis est toute embuée. Un doigt y a dessiné un petit rond. Ça sent le thym et la terre chaude. Une abeille passe près du romarin. Les pots sont encore humides. Papa arrose les pots. L'eau fait un bruit fin. Maman pose un chapeau de paille. Le chapeau sent le soleil. Tu as vu le rond, Nina ? Il est sur la buée. Le thym sent fort, hein ? Oui, maman. Je veux planter un haricot. Sous le châssis. Un haricot à lui, tout seul ? Oui. Dans un petit trou. En ce moment, Nina s'agenouille. La petite pelle est lisse. Le haricot est dans sa poche. Il fait un petit bruit. Raphaël est déjà là. Il parle peu. Il regarde une coccinelle sur le rebord. La coccinelle est rouge et ronde. Nina a envie de tout expliquer. On peut attendre. Tu peux tendre un jouet. Nina tient la petite pelle. Raphaël ne dit rien.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Une goutte tiède pend au romarin. Elle tremble, puis tient. Elle est chaude, papa. Tu la vois, Nina ? Oui, papa. Les tomates sont vertes, sous les feuilles. Elles sont dures, maman. Tu les as touchées, Nina ? Oui, maman. Sur une feuille, un &lt;emphasis level="moderate"&gt;éclat de romarin&lt;/emphasis&gt; brille. Il brille, papa. Tu le vois, le petit point ? Oui, un petit point. Ça sent le thym, tout près. Ça pique le nez. Le thym est fort, Nina ? Oui, maman. Une abeille passe près des tomates. Elle fait un bruit, papa. Près des fleurs ? Oui, tout près. Le seau bleu attend au bord de la terre. Le plastique est tiède, contre la paume. Il est chaud, maman. Tu le tiens, Nina ? Oui. En ce moment, Nina pose le seau. Je veux le seau, maintenant ! Pour les tomates, tout de suite. De l'eau, là ? Oui, de l'eau. Le seau bleu est plein ? Presque. Raphaël arrive près des pots. Il marche sans bruit. Tu verses avec moi ? Raphaël ne dit rien. Il regarde ses mains. Nina a envie de tout expliquer. Les mots montent très vite. Le seau ! L'eau ! Les tomates ! Nina pousse trop vite vers lui. Le seau penche. L'eau tombe sur la terre. Oh. Le sourire de Nina disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Ses épaules tombent un peu. Papa s'accroupit à la même hauteur. Tu vois Raphaël, Nina ? Oui, papa. Tes mains tiennent le seau, Nina ? Un peu, maman. L'éclat de romarin tremble, puis tient. Raphaël reste près des pots. Il ne dit rien, papa. Nina regarde papa.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Faustine est au jardin avec maman. Marceau est près du bac. Il parle peu. Faustine veut jouer. Maman dit : on peut &lt;emphasis&gt;attendre&lt;/emphasis&gt;. On n'imite pas. On peut tendre un jouet. On ne force pas la parole. Faustine tend le seau. Elle attend. Marceau touche le seau. Il ne dit rien. Faustine sourit. Elle ne force pas la parole. Plus tard, Marceau dit : sable. [pause]</t>
+          <t>Une goutte tiède pend au romarin. Elle tremble, puis tient. Elle est chaude, papa. Tu la vois, Nina ? Oui, papa. Les tomates sont vertes, sous les feuilles. Elles sont dures, maman. Tu les as touchées, Nina ? Oui, maman. Sur une feuille, un &lt;emphasis&gt;éclat de romarin&lt;/emphasis&gt; brille. Il brille, papa. Tu le vois, le petit point ? Oui, un petit point. Ça sent le thym, tout près. Ça pique le nez. Le thym est fort, Nina ? Oui, maman. Une abeille passe près des tomates. Elle fait un bruit, papa. Près des fleurs ? Oui, tout près. Le seau bleu attend au bord de la terre. Le plastique est tiède, contre la paume. Il est chaud, maman. Tu le tiens, Nina ? Oui. En ce moment, Nina pose le seau. Je veux le seau, maintenant ! Pour les tomates, tout de suite. De l'eau, là ? Oui, de l'eau. Le seau bleu est plein ? Presque. Raphaël arrive près des pots. Il marche sans bruit. Tu verses avec moi ? Raphaël ne dit rien. Il regarde ses mains. Nina a envie de tout expliquer. Les mots montent très vite. Le seau ! L'eau ! Les tomates ! Nina pousse trop vite vers lui. Le seau penche. L'eau tombe sur la terre. Oh. Le sourire de Nina disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Ses épaules tombent un peu. Papa s'accroupit à la même hauteur. Tu vois Raphaël, Nina ? Oui, papa. Tes mains tiennent le seau, Nina ? Un peu, maman. L'éclat de romarin tremble, puis tient. Raphaël reste près des pots. Il ne dit rien, papa. Nina regarde papa. [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1280,30 +1280,30 @@
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>attendre</t>
+          <t>éclat de romarin</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.36</v>
       </c>
       <c r="AO2" s="2" t="inlineStr"/>
       <c r="AP2" s="2" t="inlineStr">
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AS2" s="2" t="n">
         <v>100</v>
@@ -1326,40 +1326,77 @@
       <c r="AU2" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>arc=installation; intention=émerveiller puis tendre; emotion=impatience puis découragement; intensite=2; destinataire=enfant; sous_texte=elle_veut_le_seau_maintenant; tempo=naturel puis resserré; sourire=léger puis aucun; respiration=ample puis retenue</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|La vitre du châssis est toute embuée.
-narrateur|Un doigt y a dessiné un petit rond.
-narrateur|Ça sent le thym et la terre chaude.
-narrateur|Une abeille passe près du romarin.
-narrateur|Les pots sont encore humides.
-narrateur|Papa arrose les pots.
-narrateur|L'eau fait un bruit fin.
-narrateur|Maman pose un chapeau de paille.
-narrateur|Le chapeau sent le soleil.
-papa|Tu as vu le rond, Nina ?
-enfant-f|Il est sur la buée.
-maman|Le thym sent fort, hein ?
+          <t>narrateur|Une goutte tiède pend au romarin.
+narrateur|Elle tremble, puis tient.
+enfant-f|Elle est chaude, papa.
+papa|Tu la vois, Nina ?
+enfant-f|Oui, papa.
+narrateur|Les tomates sont vertes, sous les feuilles.
+enfant-f|Elles sont dures, maman.
+maman|Tu les as touchées, Nina ?
 enfant-f|Oui, maman.
-enfant-f|Je veux planter un haricot.
-enfant-f|Sous le châssis.
-papa|Un haricot à lui, tout seul ?
+narrateur|Sur une feuille, un éclat de romarin brille.
+enfant-f|Il brille, papa.
+papa|Tu le vois, le petit point ?
+enfant-f|Oui, un petit point.
+narrateur|Ça sent le thym, tout près.
+enfant-f|Ça pique le nez.
+maman|Le thym est fort, Nina ?
+enfant-f|Oui, maman.
+narrateur|Une abeille passe près des tomates.
+enfant-f|Elle fait un bruit, papa.
+papa|Près des fleurs ?
+enfant-f|Oui, tout près.
+narrateur|Le seau bleu attend au bord de la terre.
+narrateur|Le plastique est tiède, contre la paume.
+enfant-f|Il est chaud, maman.
+maman|Tu le tiens, Nina ?
 enfant-f|Oui.
-enfant-f|Dans un petit trou.
-narrateur|En ce moment, Nina s'agenouille.
-narrateur|La petite pelle est lisse.
-narrateur|Le haricot est dans sa poche.
-narrateur|Il fait un petit bruit.
-narrateur|Raphaël est déjà là.
-narrateur|Il parle peu.
-narrateur|Il regarde une coccinelle sur le rebord.
-narrateur|La coccinelle est rouge et ronde.
+narrateur|En ce moment, Nina pose le seau.
+enfant-f|Je veux le seau, maintenant !
+enfant-f|Pour les tomates, tout de suite.
+papa|De l'eau, là ?
+enfant-f|Oui, de l'eau.
+maman|Le seau bleu est plein ?
+enfant-f|Presque.
+narrateur|Raphaël arrive près des pots.
+narrateur|Il marche sans bruit.
+enfant-f|Tu verses avec moi ?
+narrateur|Raphaël ne dit rien.
+narrateur|Il regarde ses mains.
 narrateur|Nina a envie de tout expliquer.
-maman|On peut attendre.
-papa|Tu peux tendre un jouet.
-narrateur|Nina tient la petite pelle.
-narrateur|Raphaël ne dit rien.</t>
+narrateur|Les mots montent très vite.
+enfant-f|Le seau !
+enfant-f|L'eau !
+enfant-f|Les tomates !
+narrateur|Nina pousse trop vite vers lui.
+narrateur|Le seau penche.
+narrateur|L'eau tombe sur la terre.
+enfant-f|Oh.
+narrateur|Le sourire de Nina disparaît.
+narrateur|Dans sa poitrine, l'envie et l'inquiétude se bousculent.
+narrateur|Ses épaules tombent un peu.
+narrateur|Papa s'accroupit à la même hauteur.
+papa|Tu vois Raphaël, Nina ?
+enfant-f|Oui, papa.
+maman|Tes mains tiennent le seau, Nina ?
+enfant-f|Un peu, maman.
+narrateur|L'éclat de romarin tremble, puis tient.
+narrateur|Raphaël reste près des pots.
+enfant-f|Il ne dit rien, papa.
+narrateur|Nina regarde papa.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>jardin,eau</t>
         </is>
       </c>
     </row>
@@ -1391,12 +1428,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Raphaël parle peu. Que fait Nina ?</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Raphaël parle peu. Que fait &lt;emphasis level="moderate"&gt;Nina&lt;/emphasis&gt; ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Marceau parle peu. Que fait Faustine ?&lt;/slow&gt;</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Raphaël parle peu. Que fait &lt;emphasis&gt;Nina&lt;/emphasis&gt; ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1406,7 +1443,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>attendre | tendre | la pelle | un jouet | elle attend</t>
+          <t>attendre | tendre | le seau | un jouet</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1459,7 +1496,7 @@
         </is>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1470,7 +1507,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1485,34 +1522,38 @@
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="2" t="inlineStr"/>
+        <v>-2</v>
+      </c>
+      <c r="AH3" s="2" t="inlineStr">
+        <is>
+          <t>Nina</t>
+        </is>
+      </c>
       <c r="AI3" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>focused</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>rise</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AO3" s="2" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr">
@@ -1527,17 +1568,17 @@
         <v>0.86</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="AT3" s="2" t="n">
         <v>50</v>
       </c>
       <c r="AU3" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr">
         <is>
-          <t>question d'écoute, ne change pas le cours</t>
+          <t>arc=indice; intention=faire_deviner; emotion=attention; intensite=1; destinataire=enfant; sous_texte=raphael_parle_peu_que_fait_nina; tempo=suspendu; sourire=aucun; respiration=courte_avant_question</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1570,17 +1611,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nina tend la petite pelle. Pour le trou. Elle attend. Un grain de terre colle à son genou. Raphaël touche la pelle. Il ne dit rien. On ne force pas la parole. La terre n'a pas besoin de mots. Raphaël prend la pelle. Il creuse près du thym. Nina pose le haricot. Il est lisse et un peu froid. Raphaël recouvre. La terre est tiède. Elle sent le jardin. Un peu l'eau. Un peu le thym. Il est caché. Puis Raphaël dit tout bas. Haricot. Haricot. Tu as su attendre. Bravo, Nina. Papa verse un peu d'eau. La terre devient sombre. Une petite flaque brille, puis s'en va.</t>
+          <t>Nina veut le seau, tout de suite. Prends-le, maintenant ! Elle avance trop vite vers Raphaël. Les mots se bousculent dans sa bouche. Raphaël recule un peu. Il serre les mains contre lui. Oh. Le sourire ne revient pas. Nina refuse de foncer. Elle referme la bouche. Personne ne parle. Elle observe le seau, un instant. Elle écoute l'abeille près des feuilles. Tu veux l'eau avec Raphaël ? Papa reste à la même hauteur. Papa, on fait quoi ? On pose le seau, puis on reste. D'accord. Nina reste un moment, les mains ouvertes. Elle attend. Elle tend le seau. Pour toi. Raphaël ne dit rien. Il prend le seau, sans parler. Oui. Nina pose les mains sur la terre. Elle reste, sans se presser. Raphaël tient le seau, plus lentement. Merci, Nina. Papa a vu les deux, au jardin. Le plastique est tiède, sous les doigts. Il est chaud. Un peu d'eau reste au fond. Le seau. Il a de l'eau, là ? Oui, là. Nina glisse la main sur le bord. Le plastique est doux, contre la peau. Tes mains sont au chaud, Nina ? Un peu, maman. Raphaël s'assoit, puis se relève. Seau. On va jusqu'aux tomates ? Les tomates vertes sont près du thym. Oui, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Nina tend la petite pelle. Pour le trou. Elle attend. Un grain de terre colle à son genou. Raphaël touche la pelle. Il ne dit rien. On ne force pas la parole. La terre n'a pas besoin de mots. Raphaël prend la pelle. Il creuse près du thym. Nina pose le haricot. Il est lisse et un peu froid. Raphaël recouvre. La terre est tiède. Elle sent le jardin. Un peu l'eau. Un peu le thym. Il est caché. Puis Raphaël dit tout bas. Haricot. Haricot. Tu as su attendre. Bravo, Nina. Papa verse un peu d'eau. La terre devient sombre. Une petite flaque brille, puis s'en va.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nina veut le &lt;emphasis level="moderate"&gt;seau&lt;/emphasis&gt;, tout de suite. Prends-le, maintenant ! Elle avance trop vite vers Raphaël. Les mots se bousculent dans sa bouche. Raphaël recule un peu. Il serre les mains contre lui. Oh. Le sourire ne revient pas. Nina refuse de foncer. Elle referme la bouche. Personne ne parle. Elle observe le seau, un instant. Elle écoute l'abeille près des feuilles. Tu veux l'eau avec Raphaël ? Papa reste à la même hauteur. Papa, on fait quoi ? On pose le seau, puis on reste. D'accord. Nina reste un moment, les mains ouvertes. Elle attend. Elle tend le seau. Pour toi. Raphaël ne dit rien. Il prend le seau, sans parler. Oui. Nina pose les mains sur la terre. Elle reste, sans se presser. Raphaël tient le seau, plus lentement. Merci, Nina. Papa a vu les deux, au jardin. Le plastique est tiède, sous les doigts. Il est chaud. Un peu d'eau reste au fond. Le seau. Il a de l'eau, là ? Oui, là. Nina glisse la main sur le bord. Le plastique est doux, contre la peau. Tes mains sont au chaud, Nina ? Un peu, maman. Raphaël s'assoit, puis se relève. Seau. On va jusqu'aux tomates ? Les tomates vertes sont près du thym. Oui, maman.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Faustine a su &lt;emphasis&gt;attendre&lt;/emphasis&gt;. Elle a tendu un jouet. Elle n'a pas forcé la parole. [pause]</t>
+          <t>Nina veut le &lt;emphasis&gt;seau&lt;/emphasis&gt;, tout de suite. Prends-le, maintenant ! Elle avance trop vite vers Raphaël. Les mots se bousculent dans sa bouche. Raphaël recule un peu. Il serre les mains contre lui. Oh. Le sourire ne revient pas. Nina refuse de foncer. Elle referme la bouche. Personne ne parle. Elle observe le seau, un instant. Elle écoute l'abeille près des feuilles. Tu veux l'eau avec Raphaël ? Papa reste à la même hauteur. Papa, on fait quoi ? On pose le seau, puis on reste. D'accord. Nina reste un moment, les mains ouvertes. Elle attend. Elle tend le seau. Pour toi. Raphaël ne dit rien. Il prend le seau, sans parler. Oui. Nina pose les mains sur la terre. Elle reste, sans se presser. Raphaël tient le seau, plus lentement. Merci, Nina. Papa a vu les deux, au jardin. Le plastique est tiède, sous les doigts. Il est chaud. Un peu d'eau reste au fond. Le seau. Il a de l'eau, là ? Oui, là. Nina glisse la main sur le bord. Le plastique est doux, contre la peau. Tes mains sont au chaud, Nina ? Un peu, maman. Raphaël s'assoit, puis se relève. Seau. On va jusqu'aux tomates ? Les tomates vertes sont près du thym. Oui, maman. [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1627,7 +1668,7 @@
         </is>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
@@ -1635,10 +1676,10 @@
         </is>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1661,30 +1702,30 @@
       </c>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>attendre</t>
+          <t>seau</t>
         </is>
       </c>
       <c r="AI4" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>450</v>
+        <v>560</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>bright</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="AO4" s="2" t="inlineStr"/>
       <c r="AP4" s="2" t="inlineStr">
@@ -1693,10 +1734,10 @@
         </is>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AR4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AS4" s="2" t="n">
         <v>100</v>
@@ -1709,37 +1750,61 @@
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
+          <t>arc=résolution; intention=faire_vivre_le_geste; emotion=retenue puis fierté_calme; intensite=2; destinataire=enfant; sous_texte=elle_refuse_de_foncer_tend_attend; tempo=naturel; sourire=léger; respiration=relâchée</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nina tend la petite pelle.
-enfant-f|Pour le trou.
+          <t>narrateur|Nina veut le seau, tout de suite.
+enfant-f|Prends-le, maintenant !
+narrateur|Elle avance trop vite vers Raphaël.
+narrateur|Les mots se bousculent dans sa bouche.
+narrateur|Raphaël recule un peu.
+narrateur|Il serre les mains contre lui.
+enfant-f|Oh.
+narrateur|Le sourire ne revient pas.
+narrateur|Nina refuse de foncer.
+narrateur|Elle referme la bouche.
+narrateur|Personne ne parle.
+narrateur|Elle observe le seau, un instant.
+narrateur|Elle écoute l'abeille près des feuilles.
+papa|Tu veux l'eau avec Raphaël ?
+narrateur|Papa reste à la même hauteur.
+enfant-f|Papa, on fait quoi ?
+papa|On pose le seau, puis on reste.
+enfant-f|D'accord.
+narrateur|Nina reste un moment, les mains ouvertes.
 narrateur|Elle attend.
-narrateur|Un grain de terre colle à son genou.
-narrateur|Raphaël touche la pelle.
-narrateur|Il ne dit rien.
-maman|On ne force pas la parole.
-papa|La terre n'a pas besoin de mots.
-narrateur|Raphaël prend la pelle.
-narrateur|Il creuse près du thym.
-narrateur|Nina pose le haricot.
-narrateur|Il est lisse et un peu froid.
-narrateur|Raphaël recouvre.
-narrateur|La terre est tiède.
-narrateur|Elle sent le jardin.
-narrateur|Un peu l'eau.
-narrateur|Un peu le thym.
-enfant-f|Il est caché.
-narrateur|Puis Raphaël dit tout bas.
-enfant-m|Haricot.
-enfant-f|Haricot.
-papa|Tu as su attendre.
-papa|Bravo, Nina.
-narrateur|Papa verse un peu d'eau.
-narrateur|La terre devient sombre.
-narrateur|Une petite flaque brille, puis s'en va.</t>
+narrateur|Elle tend le seau.
+enfant-f|Pour toi.
+narrateur|Raphaël ne dit rien.
+narrateur|Il prend le seau, sans parler.
+copain|Oui.
+narrateur|Nina pose les mains sur la terre.
+narrateur|Elle reste, sans se presser.
+narrateur|Raphaël tient le seau, plus lentement.
+papa|Merci, Nina.
+narrateur|Papa a vu les deux, au jardin.
+maman|Le plastique est tiède, sous les doigts.
+enfant-f|Il est chaud.
+narrateur|Un peu d'eau reste au fond.
+enfant-f|Le seau.
+papa|Il a de l'eau, là ?
+enfant-f|Oui, là.
+narrateur|Nina glisse la main sur le bord.
+narrateur|Le plastique est doux, contre la peau.
+maman|Tes mains sont au chaud, Nina ?
+enfant-f|Un peu, maman.
+narrateur|Raphaël s'assoit, puis se relève.
+copain|Seau.
+enfant-f|On va jusqu'aux tomates ?
+maman|Les tomates vertes sont près du thym.
+enfant-f|Oui, maman.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>seau,eau</t>
         </is>
       </c>
     </row>
@@ -1766,17 +1831,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman essuie un peu la buée. Le rond a disparu. On voit le haricot caché, presque. Un peu d'eau, pour toi ? Raphaël secoue la tête. D'accord. D'accord. Tu as fini le trou, Nina ? Oui, maman. Le haricot est dessous. Papa ferme le robinet. L'eau s'arrête. Nina donne la main. Le chapeau de paille reste sur le banc. La coccinelle s'en va. Le thym sent encore. L'abeille s'éloigne. Le thym reste. Oui. Il sent encore.</t>
+          <t>Ils restent près des tomates. Le seau bleu penche vers une feuille. Je verse, maintenant ! Nina pousse trop vite. L'eau gicle sur le pied de Raphaël. Ça mouille ! Dis-le, Raphaël ! Raphaël serre les lèvres. Nina avance les mains, trop vite. Puis elle s'arrête net. Nina refuse de foncer, cette fois. Ses mains se ferment, puis s'ouvrent. Personne ne dit la suite. Elle observe le seau, un instant. Elle écoute le thym, tout près. Près des feuilles, un éclat de romarin luit. Là, sur le romarin. Tu prends le seau, Raphaël ? Raphaël ne dit rien. Il tend les mains, sans parler. Oui. Nina passe le seau, sans se presser. Raphaël le reçoit, plus lentement. Le plastique est lisse et tiède. Tu le vois, le seau ? Oui, papa. L'eau est tiède, Nina ? Oui, maman. Raphaël verse, un filet mince. La terre devient sombre, sous les tomates. La terre boit, Nina ? Oui, papa. Un rayon passe sur le romarin. Il allume la feuille.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Maman essuie un peu la buée. Le rond a disparu. On voit le haricot caché, presque. Un peu d'eau, pour toi ? Raphaël secoue la tête. D'accord. D'accord. Tu as fini le trou, Nina ? Oui, maman. Le haricot est dessous. Papa ferme le robinet. L'eau s'arrête. Nina donne la main. Le chapeau de paille reste sur le banc. La coccinelle s'en va. Le thym sent encore. L'abeille s'éloigne. Le thym reste. Oui. Il sent encore.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Ils restent près des tomates. Le seau bleu penche vers une feuille. Je verse, maintenant ! Nina pousse trop vite. L'eau gicle sur le pied de Raphaël. Ça mouille ! Dis-le, Raphaël ! Raphaël serre les lèvres. Nina avance les mains, trop vite. Puis elle s'arrête net. Nina refuse de foncer, cette fois. Ses mains se ferment, puis s'ouvrent. Personne ne dit la suite. Elle observe le seau, un instant. Elle écoute le thym, tout près. Près des feuilles, un &lt;emphasis level="moderate"&gt;éclat de romarin&lt;/emphasis&gt; luit. Là, sur le romarin. Tu prends le seau, Raphaël ? Raphaël ne dit rien. Il tend les mains, sans parler. Oui. Nina passe le seau, sans se presser. Raphaël le reçoit, plus lentement. Le plastique est lisse et tiède. Tu le vois, le seau ? Oui, papa. L'eau est tiède, Nina ? Oui, maman. Raphaël verse, un filet mince. La terre devient sombre, sous les tomates. La terre boit, Nina ? Oui, papa. Un rayon passe sur le romarin. Il allume la feuille.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Maman range le seau. Faustine donne la &lt;emphasis&gt;main&lt;/emphasis&gt;. [pause]</t>
+          <t>Ils restent près des tomates. Le seau bleu penche vers une feuille. Je verse, maintenant ! Nina pousse trop vite. L'eau gicle sur le pied de Raphaël. Ça mouille ! Dis-le, Raphaël ! Raphaël serre les lèvres. Nina avance les mains, trop vite. Puis elle s'arrête net. Nina refuse de foncer, cette fois. Ses mains se ferment, puis s'ouvrent. Personne ne dit la suite. Elle observe le seau, un instant. Elle écoute le thym, tout près. Près des feuilles, un &lt;emphasis&gt;éclat de romarin&lt;/emphasis&gt; luit. Là, sur le romarin. Tu prends le seau, Raphaël ? Raphaël ne dit rien. Il tend les mains, sans parler. Oui. Nina passe le seau, sans se presser. Raphaël le reçoit, plus lentement. Le plastique est lisse et tiède. Tu le vois, le seau ? Oui, papa. L'eau est tiède, Nina ? Oui, maman. Raphaël verse, un filet mince. La terre devient sombre, sous les tomates. La terre boit, Nina ? Oui, papa. Un rayon passe sur le romarin. Il allume la feuille. [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1823,7 +1888,7 @@
         </is>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
@@ -1831,10 +1896,10 @@
         </is>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1857,30 +1922,30 @@
       </c>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>éclat de romarin</t>
         </is>
       </c>
       <c r="AI5" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>lively</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.333</v>
+        <v>0.37</v>
       </c>
       <c r="AO5" s="2" t="inlineStr"/>
       <c r="AP5" s="2" t="inlineStr">
@@ -1889,10 +1954,10 @@
         </is>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AS5" s="2" t="n">
         <v>100</v>
@@ -1903,29 +1968,52 @@
       <c r="AU5" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>arc=action; intention=entraîner; emotion=élan puis prudence; intensite=2; destinataire=enfant; sous_texte=eau_trop_vite_dis_le_elle_s_arrete; tempo=vif puis posé; sourire=léger; respiration=courte</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman essuie un peu la buée.
-narrateur|Le rond a disparu.
-narrateur|On voit le haricot caché, presque.
-maman|Un peu d'eau, pour toi ?
-narrateur|Raphaël secoue la tête.
-enfant-f|D'accord.
-papa|D'accord.
-maman|Tu as fini le trou, Nina ?
+          <t>narrateur|Ils restent près des tomates.
+narrateur|Le seau bleu penche vers une feuille.
+enfant-f|Je verse, maintenant !
+narrateur|Nina pousse trop vite.
+narrateur|L'eau gicle sur le pied de Raphaël.
+enfant-f|Ça mouille !
+enfant-f|Dis-le, Raphaël !
+narrateur|Raphaël serre les lèvres.
+narrateur|Nina avance les mains, trop vite.
+narrateur|Puis elle s'arrête net.
+narrateur|Nina refuse de foncer, cette fois.
+narrateur|Ses mains se ferment, puis s'ouvrent.
+narrateur|Personne ne dit la suite.
+narrateur|Elle observe le seau, un instant.
+narrateur|Elle écoute le thym, tout près.
+narrateur|Près des feuilles, un éclat de romarin luit.
+enfant-f|Là, sur le romarin.
+enfant-f|Tu prends le seau, Raphaël ?
+narrateur|Raphaël ne dit rien.
+narrateur|Il tend les mains, sans parler.
+copain|Oui.
+narrateur|Nina passe le seau, sans se presser.
+narrateur|Raphaël le reçoit, plus lentement.
+narrateur|Le plastique est lisse et tiède.
+papa|Tu le vois, le seau ?
+enfant-f|Oui, papa.
+maman|L'eau est tiède, Nina ?
 enfant-f|Oui, maman.
-enfant-f|Le haricot est dessous.
-narrateur|Papa ferme le robinet.
-narrateur|L'eau s'arrête.
-narrateur|Nina donne la main.
-narrateur|Le chapeau de paille reste sur le banc.
-papa|La coccinelle s'en va.
-narrateur|Le thym sent encore.
-narrateur|L'abeille s'éloigne.
-enfant-f|Le thym reste.
-papa|Oui.
-papa|Il sent encore.</t>
+narrateur|Raphaël verse, un filet mince.
+narrateur|La terre devient sombre, sous les tomates.
+papa|La terre boit, Nina ?
+enfant-f|Oui, papa.
+maman|Un rayon passe sur le romarin.
+enfant-f|Il allume la feuille.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>eau,tomates</t>
         </is>
       </c>
     </row>
@@ -1952,17 +2040,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le haricot est sous la terre. Sous le châssis. Il a de l'eau, maintenant.</t>
+          <t>Ils restent près des tomates. Le seau est vide, Nina ? Oui, maman. Tu souffles un peu ? Oui, papa. Nina souffle, un filet d'air. Le plastique sent bon. Tu le sens, le seau ? Oui, maman. La terre reste un peu, sombre. Elle a bu, sous les tomates. Seau. Le seau bleu fait de l'ombre. L'abeille s'éloigne, sans bruit. On y remet de l'eau, après. Un éclat de romarin tient près des tomates.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Le haricot est sous la terre. Sous le châssis. Il a de l'eau, maintenant.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Ils restent près des tomates. Le seau est vide, Nina ? Oui, maman. Tu souffles un peu ? Oui, papa. Nina souffle, un filet d'air. Le plastique sent bon. Tu le sens, le seau ? Oui, maman. La terre reste un peu, sombre. Elle a bu, sous les tomates. Seau. Le seau bleu fait de l'ombre. L'abeille s'éloigne, sans bruit. On y remet de l'eau, après. Un &lt;emphasis level="moderate"&gt;éclat de romarin&lt;/emphasis&gt; tient près des tomates.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Ils restent près des tomates. Le seau est vide, Nina ? Oui, maman. Tu souffles un peu ? Oui, papa. Nina souffle, un filet d'air. Le plastique sent bon. Tu le sens, le seau ? Oui, maman. La terre reste un peu, sombre. Elle a bu, sous les tomates. Seau. Le seau bleu fait de l'ombre. L'abeille s'éloigne, sans bruit. On y remet de l'eau, après. Un &lt;emphasis&gt;éclat de romarin&lt;/emphasis&gt; tient près des tomates.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2009,15 +2097,15 @@
         </is>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AB6" s="2" t="n">
         <v>1.28</v>
@@ -2029,12 +2117,12 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>-2st</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>lower-pitch</t>
+          <t>low-pitch</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
@@ -2043,17 +2131,21 @@
         </is>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH6" s="2" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>éclat de romarin</t>
+        </is>
+      </c>
       <c r="AI6" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
@@ -2062,11 +2154,11 @@
       </c>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>fall</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="AO6" s="2" t="inlineStr"/>
       <c r="AP6" s="2" t="inlineStr">
@@ -2075,26 +2167,48 @@
         </is>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AU6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV6" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>arc=retour; intention=refermer; emotion=tendresse_et_fierté_calme; intensite=1; destinataire=enfant; sous_texte=l_eclat_du_debut_tient_pres_des_tomates; tempo=posé; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-f|Le haricot est sous la terre.
-maman|Sous le châssis.
-papa|Il a de l'eau, maintenant.</t>
+          <t>narrateur|Ils restent près des tomates.
+maman|Le seau est vide, Nina ?
+enfant-f|Oui, maman.
+papa|Tu souffles un peu ?
+enfant-f|Oui, papa.
+narrateur|Nina souffle, un filet d'air.
+enfant-f|Le plastique sent bon.
+maman|Tu le sens, le seau ?
+enfant-f|Oui, maman.
+papa|La terre reste un peu, sombre.
+enfant-f|Elle a bu, sous les tomates.
+copain|Seau.
+narrateur|Le seau bleu fait de l'ombre.
+narrateur|L'abeille s'éloigne, sans bruit.
+enfant-f|On y remet de l'eau, après.
+narrateur|Un éclat de romarin tient près des tomates.</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>jardin,romarin</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2172,6 +2286,13 @@
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
